--- a/human_resources_forms/002_stakeholder_survey--human_resources_forms.xlsx
+++ b/human_resources_forms/002_stakeholder_survey--human_resources_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>name_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>stakeholder_name</t>
+          <t>Name 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -796,12 +796,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>name_3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>stakeholder_name</t>
+          <t>Name 3</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>phone_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>Phone 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -849,8 +849,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="33" customWidth="1" min="2" max="2"/>
+    <col width="33" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -878,12 +878,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'leadership_and_management'}</t>
+          <t>leadership_and_management</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Leadership and management'}</t>
+          <t>Leadership and management</t>
         </is>
       </c>
     </row>
@@ -895,12 +895,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'communication_and_collaboration'}</t>
+          <t>communication_and_collaboration</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Communication and collaboration'}</t>
+          <t>Communication and collaboration</t>
         </is>
       </c>
     </row>
@@ -912,12 +912,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'performance_and_productivity'}</t>
+          <t>performance_and_productivity</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Performance and productivity'}</t>
+          <t>Performance and productivity</t>
         </is>
       </c>
     </row>
@@ -929,12 +929,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -946,12 +946,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'leadership_and_management'}</t>
+          <t>leadership_and_management</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Leadership and management'}</t>
+          <t>Leadership and management</t>
         </is>
       </c>
     </row>
@@ -963,12 +963,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'communication_and_collaboration'}</t>
+          <t>communication_and_collaboration</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Communication and collaboration'}</t>
+          <t>Communication and collaboration</t>
         </is>
       </c>
     </row>
@@ -980,12 +980,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'performance_and_productivity'}</t>
+          <t>performance_and_productivity</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Performance and productivity'}</t>
+          <t>Performance and productivity</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1014,12 +1014,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1031,12 +1031,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1048,12 +1048,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1065,12 +1065,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
